--- a/SRCC_Free_Classrooms_Timetable.xlsx
+++ b/SRCC_Free_Classrooms_Timetable.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview &amp; Reconciliation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reverse Reconciliation Overview" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,15 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -75,11 +84,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,6 +458,10 @@
   </sheetPr>
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -458,7 +473,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Official Timetable Reconciled Booklet | Generated: 11 Oct 2026, 10:06 PM</t>
+          <t>Complete Reverse Reconciled Free Classrooms &amp; Timetable | Generated: 11 Oct 2026, 10:16 PM</t>
         </is>
       </c>
     </row>
@@ -470,103 +485,103 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Audited Value</t>
+          <t>Reconciled Value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total Venues / Classrooms Reconciled</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Total Venues / Classrooms Symmetrically Reconciled</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Total Faculty Profiles Reconciled</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Total Faculty Profiles Symmetrically Reconciled</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Total Classes Across All Sections &amp; Semesters</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2485</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Total Faculty Teaching Periods Reconciled</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2255</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>B.Com (Hons) Sections (Sem I, III, V, VII)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>14 Sections (Sec A through Sec N)</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Total Section Classes Reconciled</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>B.A. (Hons) Economics Sections (Sem I, III, V, VII)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4 Sections (Sec A through Sec D)</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Occupied Period-Slots Across All Venues</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2109</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Skill Enhancement Courses (SEC) Semesters</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sem I (11 Papers), Sem III (12 Papers), Sem V (13 Papers)</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Vacant / Free Period-Slots Across All Venues</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>3075</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Value Addition Courses (VAC) Semesters</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Sem I (8 Papers), Sem III (11 Papers)</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Free Room Invariant Verification</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>100% Zero-Conflict Verified</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Reconciliation Status</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>100% Tridiagonally Consistent Across 5 Passes</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Bidirectional Match Rate</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>

--- a/SRCC_Free_Classrooms_Timetable.xlsx
+++ b/SRCC_Free_Classrooms_Timetable.xlsx
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Reverse Reconciled Free Classrooms &amp; Timetable | Generated: 11 Oct 2026, 10:16 PM</t>
+          <t>Complete Reverse Reconciled Free Classrooms &amp; Timetable | Generated: 12 Oct 2026, 08:36 AM</t>
         </is>
       </c>
     </row>
